--- a/密码管理系统-步骤执行更直观/密码记录汇总.xlsx
+++ b/密码管理系统-步骤执行更直观/密码记录汇总.xlsx
@@ -169,8 +169,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_徐国明" displayName="Table_徐国明" ref="A1:H32" headerRowCount="1">
-  <autoFilter ref="A1:H32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_徐国明" displayName="Table_徐国明" ref="A1:H31" headerRowCount="1">
+  <autoFilter ref="A1:H31"/>
   <tableColumns count="8">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="功能"/>
@@ -186,8 +186,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table_高文彬" displayName="Table_高文彬" ref="A1:H22" headerRowCount="1">
-  <autoFilter ref="A1:H22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table_高文彬" displayName="Table_高文彬" ref="A1:H31" headerRowCount="1">
+  <autoFilter ref="A1:H31"/>
   <tableColumns count="8">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="功能"/>
@@ -203,8 +203,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table_石帆" displayName="Table_石帆" ref="A1:H23" headerRowCount="1">
-  <autoFilter ref="A1:H23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table_石帆" displayName="Table_石帆" ref="A1:H31" headerRowCount="1">
+  <autoFilter ref="A1:H31"/>
   <tableColumns count="8">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="功能"/>
@@ -530,7 +530,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-04-03 09:35:11</t>
+          <t>2025-04-09 10:28:47</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6">
@@ -562,7 +562,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>隐藏密码</t>
+          <t>显示密码</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31 条记录</t>
+          <t>30 条记录</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21 条记录</t>
+          <t>30 条记录</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22 条记录</t>
+          <t>30 条记录</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>password</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -731,69 +731,65 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>防火墙</t>
+          <t>test</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>用户管理</t>
+          <t>123</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>17.244.219.28</t>
+          <t>192.168.8.87</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>pcgmkd</t>
+          <t>root</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>******</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>青岛分公司</t>
-        </is>
-      </c>
+          <t>YTH-HL4z&gt;Ud7Lnx+</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>内网</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>备用账号: admin530</t>
+          <t>123</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>CentOS</t>
+          <t>HR系统</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>开发测试</t>
+          <t>配置管理</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>193.148.121.47</t>
+          <t>68.16.140.228</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>sysadmin17</t>
+          <t>user12</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password173!</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -803,291 +799,291 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>金融内网</t>
+          <t>政务外网</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>备用账号: sysadmin11</t>
+          <t>备用账号: user51</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Kubernetes</t>
+          <t>防火墙</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>权限管理</t>
+          <t>安全管控</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>109.183.102.87</t>
+          <t>14.107.33.25</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>user648</t>
+          <t>user73</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password938!</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>成都分公司</t>
+          <t>上海分公司</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>存储网</t>
+          <t>内网</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>备用账号: root17</t>
+          <t>备用账号: user65</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Git仓库</t>
+          <t>Web服务器</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>账号管理</t>
+          <t>监控告警</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>238.25.184.160</t>
+          <t>96.33.106.193</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>root35</t>
+          <t>user43</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password686!</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>成都分公司</t>
+          <t>上海分公司</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>专线网络</t>
+          <t>互联网</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>备用账号: operator31</t>
+          <t>备用账号: user87</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>HR系统</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>用户管理</t>
+          <t>系统管理</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>154.176.198.69</t>
+          <t>245.197.137.170</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>user106</t>
+          <t>user45</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password861!</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>云平台</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>测试网</t>
+          <t>政务外网</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>备用账号: user213</t>
+          <t>备用账号: user36</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>堡垒机</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>开发测试</t>
+          <t>配置管理</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>5.151.16.144</t>
+          <t>49.77.97.63</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>root73</t>
+          <t>user84</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password996!</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>成都分公司</t>
+          <t>广州分公司</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>测试网</t>
+          <t>互联网</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>备用账号: user949</t>
+          <t>备用账号: user26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>CRM系统</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>终端管理</t>
+          <t>备份恢复</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>69.145.74.209</t>
+          <t>180.221.12.106</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>zondwi</t>
+          <t>user65</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password839!</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>长沙分公司</t>
+          <t>成都分公司</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>专线网络</t>
+          <t>内网</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>备用账号: root83</t>
+          <t>备用账号: user36</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>办公电脑</t>
+          <t>堡垒机</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>容器管理</t>
+          <t>备份恢复</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>71.217.112.74</t>
+          <t>67.161.28.188</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>admin635</t>
+          <t>user38</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password647!</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>广州分公司</t>
+          <t>成都分公司</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>专线网络</t>
+          <t>内网</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>备用账号: user408</t>
+          <t>备用账号: user11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>数据库服务器</t>
+          <t>邮件服务器</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>测试环境</t>
+          <t>监控告警</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>122.108.162.147</t>
+          <t>103.204.218.35</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>operator10</t>
+          <t>user31</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password165!</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -1097,516 +1093,516 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>管理网</t>
+          <t>内网</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>备用账号: root60</t>
+          <t>备用账号: user48</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Nginx</t>
+          <t>交换机</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>用户管理</t>
+          <t>系统管理</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>132.24.1.87</t>
+          <t>137.111.29.145</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>sysadmin50</t>
+          <t>user42</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password669!</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>重庆分公司</t>
+          <t>广州分公司</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>管理网</t>
+          <t>互联网</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>备用账号: user829</t>
+          <t>备用账号: user36</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>项目管理系统</t>
+          <t>邮件服务器</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>日志审计</t>
+          <t>安全管控</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>19.206.52.70</t>
+          <t>120.154.30.27</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>admin185</t>
+          <t>user40</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password868!</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>重庆分公司</t>
+          <t>上海分公司</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>测试网</t>
+          <t>金融内网</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>备用账号: irjram</t>
+          <t>备用账号: user10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>数据库服务器</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>存储管理</t>
+          <t>备份恢复</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>85.117.18.12</t>
+          <t>39.245.243.137</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>root87</t>
+          <t>user20</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password718!</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>边缘节点</t>
+          <t>成都分公司</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>专线网络</t>
+          <t>内网</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>备用账号: user73</t>
+          <t>备用账号: user50</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>SQL Server</t>
+          <t>OA系统</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>运维支持</t>
+          <t>用户管理</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>40.79.51.58</t>
+          <t>250.94.211.152</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>root9</t>
+          <t>user37</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password602!</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>灾备中心</t>
+          <t>广州分公司</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>物联网</t>
+          <t>专线网络</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>备用账号: root12</t>
+          <t>备用账号: user35</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>域控制器</t>
+          <t>邮件服务器</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>开发环境</t>
+          <t>配置管理</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>3.54.186.183</t>
+          <t>6.19.103.230</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>sysadmin82</t>
+          <t>user2</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password302!</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>数据中心一区</t>
+          <t>上海分公司</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>物联网</t>
+          <t>内网</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>备用账号: yfxjfb</t>
+          <t>备用账号: user53</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>CentOS</t>
+          <t>HR系统</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>补丁管理</t>
+          <t>运维支持</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>82.16.220.155</t>
+          <t>65.80.107.132</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>root7</t>
+          <t>user14</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password356!</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>灾备中心</t>
+          <t>广州分公司</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>办公网</t>
+          <t>专线网络</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>备用账号: bhkbsb</t>
+          <t>备用账号: user77</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>文件服务器</t>
+          <t>OA系统</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>监控告警</t>
+          <t>开发测试</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>47.122.112.170</t>
+          <t>47.105.160.176</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>operator77</t>
+          <t>user78</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password253!</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>天津分公司</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>VPN网络</t>
+          <t>互联网</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>备用账号: admin161</t>
+          <t>备用账号: user4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Debian</t>
+          <t>堡垒机</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>安全管控</t>
+          <t>日志审计</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>19.208.118.68</t>
+          <t>102.96.252.25</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>root99</t>
+          <t>user79</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password939!</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>西安分公司</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>金融内网</t>
+          <t>互联网</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>备用账号: bervso</t>
+          <t>备用账号: user9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Kubernetes</t>
+          <t>监控系统</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>测试环境</t>
+          <t>备份恢复</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>43.107.203.227</t>
+          <t>27.8.165.191</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>oqgwdv</t>
+          <t>user24</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password673!</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>灾备中心</t>
+          <t>广州分公司</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>备份网</t>
+          <t>专线网络</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>备用账号: user256</t>
+          <t>备用账号: user13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>RHEL</t>
+          <t>邮件服务器</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>数据管理</t>
+          <t>日志审计</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>148.79.111.7</t>
+          <t>244.67.163.51</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>sysadmin64</t>
+          <t>user27</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password301!</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>数据中心二区</t>
+          <t>上海分公司</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>互联网</t>
+          <t>金融内网</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>备用账号: root63</t>
+          <t>备用账号: user26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>财务系统</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>漏洞管理</t>
+          <t>系统管理</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>3.209.183.177</t>
+          <t>171.125.43.159</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>operator89</t>
+          <t>user46</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password849!</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>重庆分公司</t>
+          <t>广州分公司</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>备份网</t>
+          <t>金融内网</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>备用账号: sysadmin42</t>
+          <t>备用账号: user76</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>示例项目</t>
+          <t>ERP系统</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>功能说明</t>
+          <t>安全管控</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>127.0.0.1</t>
+          <t>200.24.116.156</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>username</t>
+          <t>user98</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password167!</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州分公司</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>内网</t>
+          <t>专线网络</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>备注信息</t>
+          <t>备用账号: user7</t>
         </is>
       </c>
     </row>
@@ -1618,44 +1614,44 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>用户管理</t>
+          <t>数据管理</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>17.244.219.28</t>
+          <t>51.200.201.169</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>pcgmkd</t>
+          <t>user38</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password653!</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>青岛分公司</t>
+          <t>北京总部</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>内网</t>
+          <t>互联网</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>备用账号: admin530</t>
+          <t>备用账号: user97</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>CentOS</t>
+          <t>监控系统</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1665,22 +1661,22 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>193.148.121.47</t>
+          <t>16.156.104.237</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>sysadmin17</t>
+          <t>user98</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password712!</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>成都分公司</t>
+          <t>广州分公司</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -1690,34 +1686,34 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>备用账号: sysadmin11</t>
+          <t>备用账号: user93</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Kubernetes</t>
+          <t>防火墙</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>权限管理</t>
+          <t>监控告警</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>109.183.102.87</t>
+          <t>223.18.155.95</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>user648</t>
+          <t>user90</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password298!</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -1727,264 +1723,222 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>存储网</t>
+          <t>互联网</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>备用账号: root17</t>
+          <t>备用账号: user40</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Git仓库</t>
+          <t>财务系统</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>账号管理</t>
+          <t>备份恢复</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>238.25.184.160</t>
+          <t>247.98.13.113</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>root35</t>
+          <t>user56</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password494!</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>成都分公司</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>专线网络</t>
+          <t>互联网</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>备用账号: operator31</t>
+          <t>备用账号: user42</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>HR系统</t>
+          <t>堡垒机</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>用户管理</t>
+          <t>数据管理</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>154.176.198.69</t>
+          <t>234.108.222.152</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>user106</t>
+          <t>user32</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password323!</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>云平台</t>
+          <t>广州分公司</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>测试网</t>
+          <t>专线网络</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>备用账号: user213</t>
+          <t>备用账号: user55</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>堡垒机</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>开发测试</t>
+          <t>监控告警</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>5.151.16.144</t>
+          <t>86.87.93.238</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>root73</t>
+          <t>user96</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password382!</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>成都分公司</t>
+          <t>上海分公司</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>测试网</t>
+          <t>政务外网</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>备用账号: user949</t>
+          <t>备用账号: user36</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Web服务器</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>终端管理</t>
+          <t>日志审计</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>69.145.74.209</t>
+          <t>222.126.133.205</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>zondwi</t>
+          <t>user1</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password606!</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>长沙分公司</t>
+          <t>成都分公司</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>专线网络</t>
+          <t>内网</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>备用账号: root83</t>
+          <t>备用账号: user6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>办公电脑</t>
+          <t>CRM系统</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>容器管理</t>
+          <t>日志审计</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>71.217.112.74</t>
+          <t>244.5.60.56</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>admin635</t>
+          <t>user18</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password718!</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>广州分公司</t>
+          <t>上海分公司</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>专线网络</t>
+          <t>政务外网</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>备用账号: user408</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>数据库服务器</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>测试环境</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>122.108.162.147</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>operator10</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>******</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>广州分公司</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>管理网</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>备用账号: root60</t>
+          <t>备用账号: user3</t>
         </is>
       </c>
     </row>
@@ -2002,7 +1956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2080,7 +2034,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>password</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -2102,27 +2056,27 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>交换机</t>
+          <t>CRM系统</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>日志审计</t>
+          <t>备份恢复</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>11.95.20.248</t>
+          <t>138.105.226.117</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>operator98</t>
+          <t>user81</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password604!</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -2132,187 +2086,187 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>专线网络</t>
+          <t>互联网</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>备用账号: operator88</t>
+          <t>备用账号: user36</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Jenkins</t>
+          <t>CRM系统</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>容器管理</t>
+          <t>备份恢复</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>214.183.77.99</t>
+          <t>191.40.190.195</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>sysadmin19</t>
+          <t>user54</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password997!</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>成都分公司</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>生产网</t>
+          <t>内网</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>备用账号: user586</t>
+          <t>备用账号: user23</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>邮件服务器</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>中间件管理</t>
+          <t>系统管理</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>181.227.96.151</t>
+          <t>170.161.57.142</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>mbaseu</t>
+          <t>user66</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password602!</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>南京分公司</t>
+          <t>广州分公司</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>VPN网络</t>
+          <t>互联网</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>备用账号: uxckbk</t>
+          <t>备用账号: user85</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Git仓库</t>
+          <t>邮件服务器</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>虚拟化管理</t>
+          <t>监控告警</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>230.102.82.207</t>
+          <t>93.215.254.186</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>operator77</t>
+          <t>user16</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password784!</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>南京分公司</t>
+          <t>北京总部</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>VPN网络</t>
+          <t>金融内网</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>备用账号: sysadmin19</t>
+          <t>备用账号: user63</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>交换机</t>
+          <t>数据库服务器</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>备份恢复</t>
+          <t>日志审计</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>247.238.101.234</t>
+          <t>114.160.214.60</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>admin854</t>
+          <t>user43</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password181!</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>杭州分公司</t>
+          <t>广州分公司</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>物联网</t>
+          <t>政务外网</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>备用账号: root52</t>
+          <t>备用账号: user47</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>即时通讯</t>
+          <t>监控系统</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -2322,143 +2276,143 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>204.2.235.210</t>
+          <t>73.66.151.20</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>user203</t>
+          <t>user28</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password819!</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>大连分公司</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>专线网络</t>
+          <t>内网</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>备用账号: sysadmin87</t>
+          <t>备用账号: user98</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>办公电脑</t>
+          <t>财务系统</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>权限管理</t>
+          <t>用户管理</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>148.187.79.69</t>
+          <t>117.165.147.60</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>dwcklp</t>
+          <t>user67</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password543!</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>西安分公司</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>DMZ区</t>
+          <t>金融内网</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>备用账号: sysadmin30</t>
+          <t>备用账号: user23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>RHEL</t>
+          <t>Web服务器</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>终端管理</t>
+          <t>日志审计</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>167.139.75.209</t>
+          <t>185.171.33.60</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>admin106</t>
+          <t>user44</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password949!</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>厦门分公司</t>
+          <t>北京总部</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>办公网</t>
+          <t>互联网</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>备用账号: operator6</t>
+          <t>备用账号: user32</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>财务系统</t>
+          <t>交换机</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>数据库管理</t>
+          <t>数据管理</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>150.168.128.136</t>
+          <t>85.240.154.25</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>dxeaxo</t>
+          <t>user99</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password906!</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -2468,39 +2422,39 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>互联网</t>
+          <t>金融内网</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>备用账号: urankj</t>
+          <t>备用账号: user27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>腾讯云</t>
+          <t>堡垒机</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>虚拟化管理</t>
+          <t>系统管理</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>72.163.157.160</t>
+          <t>118.4.19.225</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>sysadmin78</t>
+          <t>user69</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password498!</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -2510,12 +2464,12 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>内网</t>
+          <t>专线网络</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>备用账号: operator29</t>
+          <t>备用账号: user37</t>
         </is>
       </c>
     </row>
@@ -2527,195 +2481,195 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>权限管理</t>
+          <t>配置管理</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>238.248.136.125</t>
+          <t>62.161.156.33</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>operator22</t>
+          <t>user51</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password601!</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>天津分公司</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>开发网</t>
+          <t>专线网络</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>备用账号: arqqfb</t>
+          <t>备用账号: user7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>备份系统</t>
+          <t>数据库服务器</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>漏洞管理</t>
+          <t>日志审计</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>151.232.22.2</t>
+          <t>64.245.175.131</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>sysadmin53</t>
+          <t>user62</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password825!</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>长沙分公司</t>
+          <t>成都分公司</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>测试网</t>
+          <t>专线网络</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>备用账号: operator75</t>
+          <t>备用账号: user67</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>文件服务器</t>
+          <t>CRM系统</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>备份恢复</t>
+          <t>监控告警</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>100.61.16.184</t>
+          <t>253.91.215.163</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>root60</t>
+          <t>user56</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password209!</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>灾备中心</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>VPN网络</t>
+          <t>互联网</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>备用账号: operator50</t>
+          <t>备用账号: user69</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Tomcat</t>
+          <t>数据库服务器</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>生产环境</t>
+          <t>备份恢复</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>95.157.251.124</t>
+          <t>12.83.172.27</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>pnlgwo</t>
+          <t>user24</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password480!</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>成都分公司</t>
+          <t>广州分公司</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>存储网</t>
+          <t>内网</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>备用账号: admin502</t>
+          <t>备用账号: user79</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>邮件服务器</t>
+          <t>路由器</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>数据管理</t>
+          <t>日志审计</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>84.114.204.213</t>
+          <t>186.143.234.66</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>sysadmin59</t>
+          <t>user97</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password669!</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>西安分公司</t>
+          <t>上海分公司</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -2725,160 +2679,160 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>备用账号: sysadmin47</t>
+          <t>备用账号: user96</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Zabbix</t>
+          <t>ERP系统</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>生产环境</t>
+          <t>日志审计</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>11.117.200.190</t>
+          <t>113.120.5.123</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>root1</t>
+          <t>user2</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password325!</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>西安分公司</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>DMZ区</t>
+          <t>金融内网</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>备用账号: bohapd</t>
+          <t>备用账号: user27</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Debian</t>
+          <t>Web服务器</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>灾备环境</t>
+          <t>数据管理</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>254.255.184.124</t>
+          <t>41.46.186.186</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>user149</t>
+          <t>user95</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password533!</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>长沙分公司</t>
+          <t>广州分公司</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>测试网</t>
+          <t>互联网</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>备用账号: operator82</t>
+          <t>备用账号: user32</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>交换机</t>
+          <t>文件服务器</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>生产环境</t>
+          <t>系统管理</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>58.219.114.188</t>
+          <t>21.245.134.236</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>sysadmin54</t>
+          <t>user22</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password135!</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>上海分公司</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>金融内网</t>
+          <t>政务外网</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>备用账号: root79</t>
+          <t>备用账号: user18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>数据库服务器</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>网络管理</t>
+          <t>运维支持</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>74.182.168.107</t>
+          <t>51.217.31.67</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>operator38</t>
+          <t>user71</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password920!</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -2888,54 +2842,432 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>DMZ区</t>
+          <t>金融内网</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>备用账号: sysadmin85</t>
+          <t>备用账号: user76</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>SQL Server</t>
+          <t>ERP系统</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>应用管理</t>
+          <t>日志审计</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>125.97.14.139</t>
+          <t>89.37.236.126</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>root43</t>
+          <t>user22</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password854!</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
+          <t>上海分公司</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>政务外网</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>OA系统</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>用户管理</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>204.47.17.31</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>user11</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Password292!</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>成都分公司</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>专线网络</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user62</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>监控系统</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>配置管理</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>214.90.30.72</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>user50</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Password472!</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
           <t>北京总部</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>备用账号: root21</t>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user48</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Web服务器</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>监控告警</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>23.123.95.20</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>user3</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Password593!</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>深圳分公司</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user37</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>邮件服务器</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>开发测试</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>153.20.57.85</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>user43</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Password595!</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>深圳分公司</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>专线网络</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user41</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>路由器</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>备份恢复</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>5.163.190.35</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>user41</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Password542!</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>上海分公司</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>政务外网</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user60</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>监控系统</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>备份恢复</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>184.141.80.35</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>user53</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Password147!</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>上海分公司</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>政务外网</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user13</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>路由器</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>安全管控</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>151.72.60.70</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>user74</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Password270!</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>北京总部</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>财务系统</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>用户管理</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>226.166.201.223</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>user25</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Password551!</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>成都分公司</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>专线网络</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user44</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Web服务器</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>253.112.0.166</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>user33</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Password274!</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>深圳分公司</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>专线网络</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user46</t>
         </is>
       </c>
     </row>
@@ -2953,7 +3285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3031,7 +3363,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>password</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -3053,32 +3385,32 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>腾讯云</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>安全设备管理</t>
+          <t>用户管理</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>180.110.157.31</t>
+          <t>29.40.196.224</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>sysadmin14</t>
+          <t>user24</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password173!</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>数据中心一区</t>
+          <t>广州分公司</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -3088,56 +3420,56 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>备用账号: sysadmin64</t>
+          <t>备用账号: user82</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>办公电脑</t>
+          <t>ERP系统</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>数据库管理</t>
+          <t>安全管控</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>61.58.165.164</t>
+          <t>45.120.56.10</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>sysadmin93</t>
+          <t>user29</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password627!</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>深圳分公司</t>
+          <t>上海分公司</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>办公网</t>
+          <t>政务外网</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>备用账号: sysadmin47</t>
+          <t>备用账号: user51</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>CentOS</t>
+          <t>防火墙</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -3147,59 +3479,59 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>5.212.234.174</t>
+          <t>130.117.164.204</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>padxpt</t>
+          <t>user46</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password401!</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>武汉分公司</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>DMZ区</t>
+          <t>金融内网</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>备用账号: operator88</t>
+          <t>备用账号: user19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Git仓库</t>
+          <t>OA系统</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>数据管理</t>
+          <t>用户管理</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>248.122.170.242</t>
+          <t>227.27.79.250</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>admin786</t>
+          <t>user35</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password582!</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -3209,405 +3541,417 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>内网</t>
+          <t>专线网络</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>备用账号: admin93</t>
+          <t>备用账号: user79</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>财务系统</t>
+          <t>邮件服务器</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>存储管理</t>
+          <t>数据管理</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>28.247.225.37</t>
+          <t>31.80.26.148</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>sysadmin72</t>
+          <t>user75</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password653!</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>成都分公司</t>
+          <t>广州分公司</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>存储网</t>
+          <t>专线网络</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>备用账号: sysadmin15</t>
+          <t>备用账号: user37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>项目管理系统</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>生产环境</t>
+          <t>安全管控</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>31.110.40.229</t>
+          <t>188.245.213.134</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>user332</t>
+          <t>user98</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password854!</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>数据中心二区</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>政务外网</t>
+          <t>金融内网</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>备用账号: sysadmin77</t>
+          <t>备用账号: user47</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Kubernetes</t>
+          <t>文件服务器</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>运维支持</t>
+          <t>数据管理</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>160.55.156.174</t>
+          <t>90.202.48.87</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>ydtcqz</t>
+          <t>user75</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password623!</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>数据中心二区</t>
+          <t>北京总部</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>物联网</t>
+          <t>金融内网</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>备用账号: admin146</t>
+          <t>备用账号: user57</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>视频会议</t>
+          <t>堡垒机</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>虚拟化管理</t>
+          <t>用户管理</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>76.140.19.64</t>
+          <t>70.213.252.57</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>sysadmin2</t>
+          <t>user31</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password798!</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>边缘节点</t>
+          <t>成都分公司</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>互联网</t>
+          <t>政务外网</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>备用账号: sysadmin63</t>
+          <t>备用账号: user17</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Web服务器</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>容器管理</t>
+          <t>安全管控</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>108.95.192.171</t>
+          <t>243.117.128.86</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>root95</t>
+          <t>user40</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password388!</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>云平台</t>
+          <t>广州分公司</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>办公网</t>
+          <t>互联网</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>备用账号: operator12</t>
+          <t>备用账号: user1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>OA系统</t>
+          <t>堡垒机</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>灾备环境</t>
+          <t>数据管理</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>177.159.31.14</t>
+          <t>55.24.112.175</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>sysadmin90</t>
+          <t>user19</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password439!</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>南京分公司</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>存储网</t>
+          <t>金融内网</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>备用账号: root44</t>
+          <t>备用账号: user95</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>防火墙</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>配置管理</t>
+          <t>日志审计</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>242.173.48.95</t>
+          <t>130.213.119.146</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>root50</t>
+          <t>user6</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password623!</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>南京分公司</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>内网</t>
+          <t>专线网络</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>备用账号: dhhzfq</t>
+          <t>备用账号: user36</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr"/>
+          <t>数据库服务器</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>配置管理</t>
+        </is>
+      </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>192.168.8.87</t>
+          <t>250.38.47.95</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>user89</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password303!</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>2131</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
+          <t>上海分公司</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user61</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Git仓库</t>
+          <t>ERP系统</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>灾备环境</t>
+          <t>开发测试</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>107.136.159.158</t>
+          <t>39.117.163.13</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>root42</t>
+          <t>user90</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password265!</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>南京分公司</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>办公网</t>
+          <t>内网</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>备用账号: operator95</t>
+          <t>备用账号: user21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Ubuntu</t>
+          <t>OA系统</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>密钥管理</t>
+          <t>运维支持</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>64.194.45.134</t>
+          <t>26.254.178.249</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>root84</t>
+          <t>user51</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password169!</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -3617,44 +3961,44 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>备份网</t>
+          <t>金融内网</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>备用账号: sysadmin39</t>
+          <t>备用账号: user66</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>OA系统</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>存储管理</t>
+          <t>备份恢复</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>201.193.120.237</t>
+          <t>200.226.198.171</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>sysadmin4</t>
+          <t>user22</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password265!</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>重庆分公司</t>
+          <t>北京总部</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -3664,207 +4008,207 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>备用账号: tgjymd</t>
+          <t>备用账号: user17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Debian</t>
+          <t>数据库服务器</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>系统管理</t>
+          <t>用户管理</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>182.11.217.148</t>
+          <t>35.150.184.133</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>sysadmin62</t>
+          <t>user85</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password577!</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>成都分公司</t>
+          <t>北京总部</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>生产网</t>
+          <t>专线网络</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>备用账号: admin859</t>
+          <t>备用账号: user92</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>监控系统</t>
+          <t>防火墙</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>证书管理</t>
+          <t>系统管理</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>187.44.229.196</t>
+          <t>240.159.97.189</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>sysadmin40</t>
+          <t>user70</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password143!</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>厦门分公司</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>备份网</t>
+          <t>内网</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>备用账号: operator4</t>
+          <t>备用账号: user98</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>CentOS</t>
+          <t>财务系统</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>网络管理</t>
+          <t>日志审计</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>110.44.66.14</t>
+          <t>36.71.238.209</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>user259</t>
+          <t>user69</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password156!</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>青岛分公司</t>
+          <t>成都分公司</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>政务外网</t>
+          <t>金融内网</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>备用账号: sysadmin78</t>
+          <t>备用账号: user8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>交换机</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>培训环境</t>
+          <t>数据管理</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>241.0.92.250</t>
+          <t>113.69.7.152</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>operator2</t>
+          <t>user50</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password920!</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>云平台</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>生产网</t>
+          <t>金融内网</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>备用账号: admin604</t>
+          <t>备用账号: user27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Redis</t>
+          <t>数据库服务器</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>配置管理</t>
+          <t>运维支持</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>17.105.98.131</t>
+          <t>154.10.62.194</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>admin233</t>
+          <t>user50</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password268!</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>数据中心一区</t>
+          <t>深圳分公司</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -3874,49 +4218,385 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>备用账号: admin220</t>
+          <t>备用账号: user22</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Windows Server</t>
+          <t>数据库服务器</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>测试环境</t>
+          <t>配置管理</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>225.170.1.222</t>
+          <t>135.30.64.165</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>root8</t>
+          <t>user61</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>Password298!</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>数据中心二区</t>
+          <t>广州分公司</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>专线网络</t>
+          <t>金融内网</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>备用账号: root68</t>
+          <t>备用账号: user73</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>交换机</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>日志审计</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>87.113.79.207</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>user38</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Password200!</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>深圳分公司</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>政务外网</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user68</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>CRM系统</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>日志审计</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>202.234.206.149</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>user19</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Password463!</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>广州分公司</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user38</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>ERP系统</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>开发测试</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>119.199.174.176</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>user66</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Password794!</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>上海分公司</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>金融内网</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user89</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>ERP系统</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>189.106.97.246</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>user38</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Password511!</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>北京总部</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user46</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>监控系统</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>数据管理</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>66.188.115.136</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>user4</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Password792!</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>上海分公司</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user81</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>ERP系统</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>运维支持</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>163.20.216.12</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>user33</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Password166!</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>北京总部</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>政务外网</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user23</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>防火墙</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>监控告警</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>128.84.133.147</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>user58</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Password899!</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>上海分公司</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>CRM系统</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>日志审计</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>45.63.174.200</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>user86</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Password396!</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>深圳分公司</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>备用账号: user59</t>
         </is>
       </c>
     </row>
